--- a/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_64988_completo.xlsx
+++ b/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_64988_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc22d771cdccb4705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfdc105e2552f4a8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    295.3874</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    230.9597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    261.6554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    333.2850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    287.6490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    266.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    242.4797</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    235.9505</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    258.6543</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    292.0943</x:v>
+        <x:v>    288.4105</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_64988_completo.xlsx
+++ b/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_64988_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfdc105e2552f4a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R795b71db91f64721"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    356.3379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    987.2361</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    189.8973</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    186.8045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    197.8167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    216.2547</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    256.7024</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    287.4957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    282.3390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    285.4510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    238.0602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    259.8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    335.5685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    501.4165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    290.1192</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    245.9198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    298.6415</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    318.9254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    253.5073</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    284.7328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    365.3001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    589.2989</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    428.2090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    310.5098</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    368.0067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    635.7515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    745.4081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    191.4629</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    222.2010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    247.1268</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    270.1922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    223.2613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9634</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    196.6106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    194.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    198.5717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    204.4892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    208.9584</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    215.2861</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    226.8110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    245.2161</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    267.0535</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    307.5448</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    425.6812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    652.6623</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    580.2697</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    326.6923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    242.4797</x:v>
+        <x:v>    242.0205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    665.5157</x:v>
+        <x:v>    641.7072</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1109.6435</x:v>
+        <x:v>   1222.9585</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    347.5279</x:v>
+        <x:v>    352.1055</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    317.6674</x:v>
+        <x:v>    317.7874</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    745.6588</x:v>
+        <x:v>    693.2193</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    748.2294</x:v>
+        <x:v>    786.2840</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    954.2267</x:v>
+        <x:v>    864.1313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1041.5271</x:v>
+        <x:v>   1094.6471</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1910.6346</x:v>
+        <x:v>   1929.3075</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    820.4210</x:v>
+        <x:v>    818.3728</x:v>
       </x:c>
     </x:row>
     <x:row>
